--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561996116</v>
+        <v>46157.9307091803</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9307091803</v>
+        <v>46157.93153590342</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93153590342</v>
+        <v>46157.933937037</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.933937037</v>
+        <v>46157.93708368882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708368882</v>
+        <v>46158.28210706291</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210706291</v>
+        <v>46158.29665794798</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665794798</v>
+        <v>46158.29805309624</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805309624</v>
+        <v>46158.33381440674</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381440674</v>
+        <v>46158.36847971709</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847971709</v>
+        <v>46158.37281640687</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
